--- a/week-04/Product spec drivers.xlsx
+++ b/week-04/Product spec drivers.xlsx
@@ -8,19 +8,36 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\onurkaraer\Documents\DataAnalytics\week-04\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B16A1744-8A6B-4EFC-8A29-DAAD4FB9D144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B87C13D1-A721-42C7-B270-1B4C0CA23138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D8F0F0BB-ED70-4734-8BAC-5D910C08C423}"/>
   </bookViews>
   <sheets>
-    <sheet name="data-1777491838302" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
+    <sheet name="data-1777491838302" sheetId="1" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="19" r:id="rId3"/>
+  </pivotCaches>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="102">
   <si>
     <t>item_description</t>
   </si>
@@ -308,14 +325,33 @@
   </si>
   <si>
     <t>Bacardi Rum Runner</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Sum of total_revenue</t>
+  </si>
+  <si>
+    <t>Count of item_description</t>
+  </si>
+  <si>
+    <t>AvgRevPerProdBottleSize</t>
+  </si>
+  <si>
+    <t>Bottle Size</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
@@ -750,7 +786,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -793,12 +829,20 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="42" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -826,6 +870,7 @@
     <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
     <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
     <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Currency" xfId="42" builtinId="4"/>
     <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
     <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
     <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
@@ -857,6 +902,2506 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>#</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> of SKUs and Revenues</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$A$16</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Bottle Size</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$A$17:$A$20</c:f>
+              <c:numCache>
+                <c:formatCode>@</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>375</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1750</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$A$17:$A$20</c:f>
+              <c:numCache>
+                <c:formatCode>@</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>375</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1750</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-AEDC-4768-B9E3-1190951FB640}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$D$16</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>AvgRevPerProdBottleSize</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:gradFill>
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="5000"/>
+                      <a:lumOff val="95000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="74000">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="45000"/>
+                      <a:lumOff val="55000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="83000">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="45000"/>
+                      <a:lumOff val="55000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="30000"/>
+                      <a:lumOff val="70000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="1"/>
+              </a:gradFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$A$17:$A$20</c:f>
+              <c:numCache>
+                <c:formatCode>@</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>375</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1750</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$17:$D$20</c:f>
+              <c:numCache>
+                <c:formatCode>_("$"* #,##0.00_);_("$"* \(#,##0.00\);_("$"* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>78826.224545454548</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>194508.03454545455</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>139166.74113207549</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>361530.00727272726</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-AEDC-4768-B9E3-1190951FB640}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:axId val="1026220095"/>
+        <c:axId val="1026203775"/>
+      </c:barChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$16</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Count of item_description</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$17:$C$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>22</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-AEDC-4768-B9E3-1190951FB640}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1026214815"/>
+        <c:axId val="1026216255"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1026220095"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="@" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1026203775"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1026203775"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="@" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1026220095"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1026216255"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1026214815"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:catAx>
+        <c:axId val="1026214815"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1026216255"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>204787</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>100012</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>509587</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F4C701A-64B8-59C7-8E0F-99D6C0915FDE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="onur karaer" refreshedDate="46142.580971990741" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="129" xr:uid="{E54813E3-2C5E-4C09-8A98-253DDBF5C65E}">
+  <cacheSource type="worksheet">
+    <worksheetSource name="Table1"/>
+  </cacheSource>
+  <cacheFields count="7">
+    <cacheField name="item_description" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="item_no" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1649" maxValue="943367"/>
+    </cacheField>
+    <cacheField name="pack" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="3" maxValue="120"/>
+    </cacheField>
+    <cacheField name="inner_pack" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="12"/>
+    </cacheField>
+    <cacheField name="proof" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="20" maxValue="151"/>
+    </cacheField>
+    <cacheField name="bottle_size" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="50" maxValue="1750" count="10">
+        <n v="1750"/>
+        <n v="50"/>
+        <n v="200"/>
+        <n v="1000"/>
+        <n v="100"/>
+        <n v="603"/>
+        <n v="750"/>
+        <n v="375"/>
+        <n v="600"/>
+        <n v="500"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="total_revenue" numFmtId="8">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="62.82" maxValue="3153668.04"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="129">
+  <r>
+    <s v="Bacardi Rum Runner"/>
+    <n v="904449"/>
+    <n v="6"/>
+    <n v="1"/>
+    <n v="25"/>
+    <x v="0"/>
+    <n v="62.82"/>
+  </r>
+  <r>
+    <s v="Bacardi Limon"/>
+    <n v="943131"/>
+    <n v="12"/>
+    <n v="10"/>
+    <n v="70"/>
+    <x v="1"/>
+    <n v="98.52"/>
+  </r>
+  <r>
+    <s v="Bacardi Black Razz Miniature"/>
+    <n v="943259"/>
+    <n v="120"/>
+    <n v="1"/>
+    <n v="70"/>
+    <x v="1"/>
+    <n v="99.6"/>
+  </r>
+  <r>
+    <s v="Bacardi O Rum"/>
+    <n v="902205"/>
+    <n v="24"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="2"/>
+    <n v="111.84"/>
+  </r>
+  <r>
+    <s v="Bombay Sapphire Gin"/>
+    <n v="28223"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="94"/>
+    <x v="2"/>
+    <n v="143.76"/>
+  </r>
+  <r>
+    <s v="Bacardi Torched Cherry"/>
+    <n v="943199"/>
+    <n v="6"/>
+    <n v="1"/>
+    <n v="70"/>
+    <x v="0"/>
+    <n v="144"/>
+  </r>
+  <r>
+    <s v="Castillo Gold Rum"/>
+    <n v="943357"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="3"/>
+    <n v="176.16"/>
+  </r>
+  <r>
+    <s v="Grey Goose Le Citron"/>
+    <n v="934266"/>
+    <n v="6"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="3"/>
+    <n v="198"/>
+  </r>
+  <r>
+    <s v="Grey Goose Le Melon"/>
+    <n v="933673"/>
+    <n v="6"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="3"/>
+    <n v="198"/>
+  </r>
+  <r>
+    <s v="Grey Goose L'Orange"/>
+    <n v="934437"/>
+    <n v="6"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="3"/>
+    <n v="198"/>
+  </r>
+  <r>
+    <s v="Grey Goose La Poire"/>
+    <n v="934603"/>
+    <n v="6"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="3"/>
+    <n v="198"/>
+  </r>
+  <r>
+    <s v="Bombay Sapphire Gin"/>
+    <n v="928223"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="94"/>
+    <x v="2"/>
+    <n v="216"/>
+  </r>
+  <r>
+    <s v="Bacardi Gold Rum"/>
+    <n v="902966"/>
+    <n v="48"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="4"/>
+    <n v="316.8"/>
+  </r>
+  <r>
+    <s v="Bacardi Big Apple Rum"/>
+    <n v="904872"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="70"/>
+    <x v="3"/>
+    <n v="378"/>
+  </r>
+  <r>
+    <s v="Castillo Spiced Rum"/>
+    <n v="943367"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="70"/>
+    <x v="3"/>
+    <n v="440.4"/>
+  </r>
+  <r>
+    <s v="Cazadores Reposado"/>
+    <n v="904808"/>
+    <n v="6"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="0"/>
+    <n v="528.72"/>
+  </r>
+  <r>
+    <s v="Dewar's White Label Scotch Mini"/>
+    <n v="902365"/>
+    <n v="10"/>
+    <n v="12"/>
+    <n v="86"/>
+    <x v="5"/>
+    <n v="537.9"/>
+  </r>
+  <r>
+    <s v="Bacardi Coco"/>
+    <n v="904541"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="70"/>
+    <x v="6"/>
+    <n v="600"/>
+  </r>
+  <r>
+    <s v="Dewars White Label Scotch"/>
+    <n v="902835"/>
+    <n v="48"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="2"/>
+    <n v="624"/>
+  </r>
+  <r>
+    <s v="Bombay Sapphire Gin"/>
+    <n v="902979"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="7"/>
+    <n v="682.08"/>
+  </r>
+  <r>
+    <s v="Bacardi Pineapple Fusion"/>
+    <n v="43142"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="70"/>
+    <x v="7"/>
+    <n v="810"/>
+  </r>
+  <r>
+    <s v="Oxley Dry Gin"/>
+    <n v="927957"/>
+    <n v="6"/>
+    <n v="1"/>
+    <n v="94"/>
+    <x v="3"/>
+    <n v="900"/>
+  </r>
+  <r>
+    <s v="Bacardi Mango Fusion"/>
+    <n v="43092"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="70"/>
+    <x v="7"/>
+    <n v="1014"/>
+  </r>
+  <r>
+    <s v="Bombay Sapphire Gin Minis"/>
+    <n v="902282"/>
+    <n v="10"/>
+    <n v="12"/>
+    <n v="94"/>
+    <x v="1"/>
+    <n v="1200"/>
+  </r>
+  <r>
+    <s v="Grey Goose La Poire Mini"/>
+    <n v="34684"/>
+    <n v="10"/>
+    <n v="12"/>
+    <n v="80"/>
+    <x v="8"/>
+    <n v="1200"/>
+  </r>
+  <r>
+    <s v="Grey Goose Le Citron Mini"/>
+    <n v="34269"/>
+    <n v="10"/>
+    <n v="12"/>
+    <n v="80"/>
+    <x v="8"/>
+    <n v="1260"/>
+  </r>
+  <r>
+    <s v="Bacardi Dragonberry"/>
+    <n v="43052"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="70"/>
+    <x v="7"/>
+    <n v="1266"/>
+  </r>
+  <r>
+    <s v="Nassau Royale"/>
+    <n v="904642"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="68"/>
+    <x v="3"/>
+    <n v="1346.88"/>
+  </r>
+  <r>
+    <s v="Bacardi Rock Coconut"/>
+    <n v="943183"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="70"/>
+    <x v="6"/>
+    <n v="1500"/>
+  </r>
+  <r>
+    <s v="St Germain"/>
+    <n v="66834"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="40"/>
+    <x v="2"/>
+    <n v="1695.75"/>
+  </r>
+  <r>
+    <s v="Cazadores Blanco"/>
+    <n v="904000"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="6"/>
+    <n v="1815.84"/>
+  </r>
+  <r>
+    <s v="Corzo Anejo Tequila"/>
+    <n v="902975"/>
+    <n v="6"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="6"/>
+    <n v="1951.32"/>
+  </r>
+  <r>
+    <s v="Bacardi 8 w/2 Glasses"/>
+    <n v="1649"/>
+    <n v="6"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="6"/>
+    <n v="2126.25"/>
+  </r>
+  <r>
+    <s v="St. Germain Mini"/>
+    <n v="66835"/>
+    <n v="4"/>
+    <n v="12"/>
+    <n v="40"/>
+    <x v="8"/>
+    <n v="2207.52"/>
+  </r>
+  <r>
+    <s v="Bacardi 8 Gift Box"/>
+    <n v="4071"/>
+    <n v="6"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="6"/>
+    <n v="2268"/>
+  </r>
+  <r>
+    <s v="Bacardi Grand Melon Rum"/>
+    <n v="904512"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="70"/>
+    <x v="3"/>
+    <n v="2396.16"/>
+  </r>
+  <r>
+    <s v="Bacardi Anejo Mex Rum"/>
+    <n v="903796"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="6"/>
+    <n v="2512.08"/>
+  </r>
+  <r>
+    <s v="Bacardi 1873 Solera"/>
+    <n v="903331"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="6"/>
+    <n v="2609.2800000000002"/>
+  </r>
+  <r>
+    <s v="Bombay Original Gin"/>
+    <n v="28208"/>
+    <n v="6"/>
+    <n v="1"/>
+    <n v="86"/>
+    <x v="0"/>
+    <n v="2921.25"/>
+  </r>
+  <r>
+    <s v="Grey Goose Le Melon Mini"/>
+    <n v="33670"/>
+    <n v="10"/>
+    <n v="12"/>
+    <n v="80"/>
+    <x v="8"/>
+    <n v="3090"/>
+  </r>
+  <r>
+    <s v="Benedictine Liqueur Dom"/>
+    <n v="902243"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="6"/>
+    <n v="3483"/>
+  </r>
+  <r>
+    <s v="Bacardi Oakheart PET"/>
+    <n v="43204"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="70"/>
+    <x v="6"/>
+    <n v="3832.5"/>
+  </r>
+  <r>
+    <s v="Bacardi Pineapple Fusion PET"/>
+    <n v="43135"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="70"/>
+    <x v="6"/>
+    <n v="3912"/>
+  </r>
+  <r>
+    <s v="St. Germain w/Carafe"/>
+    <n v="3891"/>
+    <n v="6"/>
+    <n v="1"/>
+    <n v="40"/>
+    <x v="6"/>
+    <n v="3948.75"/>
+  </r>
+  <r>
+    <s v="Bacardi Cocktails Strawberry Daiquiri Light"/>
+    <n v="56870"/>
+    <n v="6"/>
+    <n v="1"/>
+    <n v="30"/>
+    <x v="0"/>
+    <n v="4272"/>
+  </r>
+  <r>
+    <s v="Grey Goose Cherry Noir"/>
+    <n v="35933"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="7"/>
+    <n v="5533.2"/>
+  </r>
+  <r>
+    <s v="Bacardi Dragon Berry PET"/>
+    <n v="43055"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="70"/>
+    <x v="6"/>
+    <n v="6084"/>
+  </r>
+  <r>
+    <s v="Bacardi Oakheart w/Stein"/>
+    <n v="3326"/>
+    <n v="6"/>
+    <n v="1"/>
+    <n v="70"/>
+    <x v="6"/>
+    <n v="8046"/>
+  </r>
+  <r>
+    <s v="Drambuie w/Pitcher"/>
+    <n v="4079"/>
+    <n v="6"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="6"/>
+    <n v="8640"/>
+  </r>
+  <r>
+    <s v="Bacardi Oakheart Mini"/>
+    <n v="43201"/>
+    <n v="12"/>
+    <n v="10"/>
+    <n v="70"/>
+    <x v="9"/>
+    <n v="9719.58"/>
+  </r>
+  <r>
+    <s v="D'usse VSOP"/>
+    <n v="47863"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="7"/>
+    <n v="10367.73"/>
+  </r>
+  <r>
+    <s v="Dewars White Label Scotch"/>
+    <n v="4864"/>
+    <n v="24"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="7"/>
+    <n v="10577.98"/>
+  </r>
+  <r>
+    <s v="Castillo Spiced Rum"/>
+    <n v="43366"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="70"/>
+    <x v="6"/>
+    <n v="12305.28"/>
+  </r>
+  <r>
+    <s v="Bacardi Mango Fusion Mini"/>
+    <n v="43089"/>
+    <n v="12"/>
+    <n v="10"/>
+    <n v="70"/>
+    <x v="9"/>
+    <n v="13755.22"/>
+  </r>
+  <r>
+    <s v="D'usse VSOP"/>
+    <n v="47865"/>
+    <n v="6"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="6"/>
+    <n v="16272"/>
+  </r>
+  <r>
+    <s v="Dewar's Highlander Honey"/>
+    <n v="64888"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="6"/>
+    <n v="16454.48"/>
+  </r>
+  <r>
+    <s v="Bacardi Gold Rum PET"/>
+    <n v="43040"/>
+    <n v="6"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="0"/>
+    <n v="18327"/>
+  </r>
+  <r>
+    <s v="Bacardi Arctic Grape Liqueur"/>
+    <n v="43163"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="70"/>
+    <x v="6"/>
+    <n v="19786.560000000001"/>
+  </r>
+  <r>
+    <s v="Bacardi Limon"/>
+    <n v="43134"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="70"/>
+    <x v="7"/>
+    <n v="23794.12"/>
+  </r>
+  <r>
+    <s v="Bacardi 8 Rum"/>
+    <n v="42370"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="6"/>
+    <n v="24396.51"/>
+  </r>
+  <r>
+    <s v="Bacardi Torched Cherry"/>
+    <n v="43198"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="70"/>
+    <x v="3"/>
+    <n v="24792.83"/>
+  </r>
+  <r>
+    <s v="Grey Goose La Poire Vodka"/>
+    <n v="34605"/>
+    <n v="6"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="6"/>
+    <n v="25215.66"/>
+  </r>
+  <r>
+    <s v="Bacardi Wolf Berry"/>
+    <n v="43210"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="70"/>
+    <x v="6"/>
+    <n v="25660.25"/>
+  </r>
+  <r>
+    <s v="Grey Goose Night Vision"/>
+    <n v="4029"/>
+    <n v="6"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="3"/>
+    <n v="28314"/>
+  </r>
+  <r>
+    <s v="Bacardi Classic Cocktails Strawberry Daiquiri"/>
+    <n v="57092"/>
+    <n v="6"/>
+    <n v="1"/>
+    <n v="30"/>
+    <x v="0"/>
+    <n v="29295.5"/>
+  </r>
+  <r>
+    <s v="Castillo Silver Rum"/>
+    <n v="43386"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="6"/>
+    <n v="30463.68"/>
+  </r>
+  <r>
+    <s v="Bacardi Party Drinks Hurricane"/>
+    <n v="56840"/>
+    <n v="6"/>
+    <n v="1"/>
+    <n v="25"/>
+    <x v="0"/>
+    <n v="32372.86"/>
+  </r>
+  <r>
+    <s v="Grey Goose Le Citron"/>
+    <n v="34267"/>
+    <n v="6"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="6"/>
+    <n v="33204.78"/>
+  </r>
+  <r>
+    <s v="Bacardi Classic Cocktails Mojito"/>
+    <n v="56828"/>
+    <n v="6"/>
+    <n v="1"/>
+    <n v="30"/>
+    <x v="0"/>
+    <n v="33608"/>
+  </r>
+  <r>
+    <s v="Cazadores Anejo"/>
+    <n v="89099"/>
+    <n v="6"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="6"/>
+    <n v="33763.919999999998"/>
+  </r>
+  <r>
+    <s v="Bombay Sapphire East"/>
+    <n v="28210"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="84"/>
+    <x v="6"/>
+    <n v="35767.26"/>
+  </r>
+  <r>
+    <s v="Bacardi Party Drinks Rum Island Iced Tea"/>
+    <n v="56846"/>
+    <n v="6"/>
+    <n v="1"/>
+    <n v="25"/>
+    <x v="0"/>
+    <n v="38765.24"/>
+  </r>
+  <r>
+    <s v="Bacardi Gold Rum"/>
+    <n v="43034"/>
+    <n v="24"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="7"/>
+    <n v="40553.96"/>
+  </r>
+  <r>
+    <s v="Bacardi O"/>
+    <n v="43116"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="70"/>
+    <x v="6"/>
+    <n v="45446.35"/>
+  </r>
+  <r>
+    <s v="Bacardi Black Razz"/>
+    <n v="43263"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="70"/>
+    <x v="3"/>
+    <n v="46035"/>
+  </r>
+  <r>
+    <s v="Bacardi Party Drinks Zombie"/>
+    <n v="56843"/>
+    <n v="6"/>
+    <n v="1"/>
+    <n v="25"/>
+    <x v="0"/>
+    <n v="49953.11"/>
+  </r>
+  <r>
+    <s v="Bacardi Party Drinks Bahama Mama"/>
+    <n v="56850"/>
+    <n v="6"/>
+    <n v="1"/>
+    <n v="20"/>
+    <x v="0"/>
+    <n v="50794.78"/>
+  </r>
+  <r>
+    <s v="Bacardi Gold Rum Mini"/>
+    <n v="43031"/>
+    <n v="12"/>
+    <n v="10"/>
+    <n v="80"/>
+    <x v="9"/>
+    <n v="51945.18"/>
+  </r>
+  <r>
+    <s v="Grey Goose Vodka L'orange"/>
+    <n v="34436"/>
+    <n v="6"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="6"/>
+    <n v="52927.92"/>
+  </r>
+  <r>
+    <s v="Dewar's 12yr"/>
+    <n v="4876"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="6"/>
+    <n v="52946.5"/>
+  </r>
+  <r>
+    <s v="Bacardi Select Rum"/>
+    <n v="43048"/>
+    <n v="6"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="0"/>
+    <n v="54906.48"/>
+  </r>
+  <r>
+    <s v="Grey Goose Le Melon"/>
+    <n v="33672"/>
+    <n v="6"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="6"/>
+    <n v="55036.160000000003"/>
+  </r>
+  <r>
+    <s v="Bacardi Gold Rum Pet"/>
+    <n v="43035"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="6"/>
+    <n v="57823.11"/>
+  </r>
+  <r>
+    <s v="Bacardi Peach Red"/>
+    <n v="43066"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="70"/>
+    <x v="6"/>
+    <n v="62914.98"/>
+  </r>
+  <r>
+    <s v="Bacardi Superior Rum"/>
+    <n v="43123"/>
+    <n v="48"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="2"/>
+    <n v="68842.5"/>
+  </r>
+  <r>
+    <s v="Grey Goose Cherry Noir"/>
+    <n v="35934"/>
+    <n v="6"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="6"/>
+    <n v="85910.78"/>
+  </r>
+  <r>
+    <s v="Bacardi Mango Fusion"/>
+    <n v="43095"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="70"/>
+    <x v="6"/>
+    <n v="87039.75"/>
+  </r>
+  <r>
+    <s v="Bacardi Black Razz"/>
+    <n v="43209"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="70"/>
+    <x v="6"/>
+    <n v="90273.75"/>
+  </r>
+  <r>
+    <s v="Grey Goose Vodka Mini"/>
+    <n v="34421"/>
+    <n v="10"/>
+    <n v="12"/>
+    <n v="80"/>
+    <x v="8"/>
+    <n v="91650"/>
+  </r>
+  <r>
+    <s v="Bacardi Pineapple Fusion"/>
+    <n v="43145"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="70"/>
+    <x v="6"/>
+    <n v="93833"/>
+  </r>
+  <r>
+    <s v="Bombay Dry Gin"/>
+    <n v="28206"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="86"/>
+    <x v="6"/>
+    <n v="95496.4"/>
+  </r>
+  <r>
+    <s v="Bacardi Select Rum"/>
+    <n v="43046"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="6"/>
+    <n v="96734.04"/>
+  </r>
+  <r>
+    <s v="Bacardi Torched Cherry"/>
+    <n v="43197"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="70"/>
+    <x v="6"/>
+    <n v="99284.27"/>
+  </r>
+  <r>
+    <s v="B&amp;b D.o.m."/>
+    <n v="64336"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="6"/>
+    <n v="110643.52"/>
+  </r>
+  <r>
+    <s v="Cazadores Reposado"/>
+    <n v="89121"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="6"/>
+    <n v="130854.39"/>
+  </r>
+  <r>
+    <s v="Castillo Silver Rum"/>
+    <n v="43388"/>
+    <n v="6"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="0"/>
+    <n v="133719.92000000001"/>
+  </r>
+  <r>
+    <s v="Bacardi Gold Rum"/>
+    <n v="43037"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="3"/>
+    <n v="136621.81"/>
+  </r>
+  <r>
+    <s v="Bacardi Dragon Berry"/>
+    <n v="43050"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="70"/>
+    <x v="3"/>
+    <n v="142477.51999999999"/>
+  </r>
+  <r>
+    <s v="Bacardi Superior Rum Mini"/>
+    <n v="43121"/>
+    <n v="12"/>
+    <n v="10"/>
+    <n v="80"/>
+    <x v="9"/>
+    <n v="144878.16"/>
+  </r>
+  <r>
+    <s v="Grey Goose w/2 Glasses &amp; Shaker"/>
+    <n v="4020"/>
+    <n v="3"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="0"/>
+    <n v="145473.93"/>
+  </r>
+  <r>
+    <s v="Bacardi O"/>
+    <n v="43117"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="70"/>
+    <x v="3"/>
+    <n v="173904.78"/>
+  </r>
+  <r>
+    <s v="Bombay Sapphire Gin"/>
+    <n v="28238"/>
+    <n v="6"/>
+    <n v="1"/>
+    <n v="94"/>
+    <x v="0"/>
+    <n v="182396.83"/>
+  </r>
+  <r>
+    <s v="St. Germain"/>
+    <n v="66836"/>
+    <n v="6"/>
+    <n v="1"/>
+    <n v="40"/>
+    <x v="6"/>
+    <n v="187809.75"/>
+  </r>
+  <r>
+    <s v="Drambuie Liqueur"/>
+    <n v="64876"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="6"/>
+    <n v="188889.60000000001"/>
+  </r>
+  <r>
+    <s v="Bacardi Oakheart"/>
+    <n v="43205"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="70"/>
+    <x v="6"/>
+    <n v="191517.39"/>
+  </r>
+  <r>
+    <s v="Bacardi Superior Rum"/>
+    <n v="43124"/>
+    <n v="24"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="7"/>
+    <n v="238584.2"/>
+  </r>
+  <r>
+    <s v="Bacardi Limon"/>
+    <n v="43138"/>
+    <n v="6"/>
+    <n v="1"/>
+    <n v="70"/>
+    <x v="0"/>
+    <n v="240530.82"/>
+  </r>
+  <r>
+    <s v="Bacardi Dragon Berry"/>
+    <n v="43051"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="70"/>
+    <x v="6"/>
+    <n v="252576.22"/>
+  </r>
+  <r>
+    <s v="Bacardi 151 Proof Rum"/>
+    <n v="43156"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="151"/>
+    <x v="6"/>
+    <n v="253154.34"/>
+  </r>
+  <r>
+    <s v="Bacardi Gold Rum"/>
+    <n v="43036"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="6"/>
+    <n v="262684.98"/>
+  </r>
+  <r>
+    <s v="Dewar's White Label Scotch"/>
+    <n v="4866"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="6"/>
+    <n v="298422.92"/>
+  </r>
+  <r>
+    <s v="Castillo Silver Rum"/>
+    <n v="43387"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="3"/>
+    <n v="298479.53999999998"/>
+  </r>
+  <r>
+    <s v="Bacardi Superior PET"/>
+    <n v="43120"/>
+    <n v="6"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="0"/>
+    <n v="353430"/>
+  </r>
+  <r>
+    <s v="Grey Goose Vodka"/>
+    <n v="34359"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="2"/>
+    <n v="355916.22"/>
+  </r>
+  <r>
+    <s v="Dewar's White Label Scotch"/>
+    <n v="4868"/>
+    <n v="6"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="0"/>
+    <n v="378470.76"/>
+  </r>
+  <r>
+    <s v="Bombay Sapphire Gin"/>
+    <n v="28236"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="94"/>
+    <x v="6"/>
+    <n v="391050.66"/>
+  </r>
+  <r>
+    <s v="Bacardi Superior Rum Pet"/>
+    <n v="43125"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="6"/>
+    <n v="397117.02"/>
+  </r>
+  <r>
+    <s v="Bacardi Gold Rum"/>
+    <n v="43038"/>
+    <n v="6"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="0"/>
+    <n v="397957.9"/>
+  </r>
+  <r>
+    <s v="Grey Goose Vodka"/>
+    <n v="34425"/>
+    <n v="6"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="0"/>
+    <n v="427277.34"/>
+  </r>
+  <r>
+    <s v="Bacardi Limon"/>
+    <n v="43136"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="70"/>
+    <x v="6"/>
+    <n v="462801.26"/>
+  </r>
+  <r>
+    <s v="Grey Goose Vodka"/>
+    <n v="34423"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="7"/>
+    <n v="533905.19999999995"/>
+  </r>
+  <r>
+    <s v="Dewar's White Label Scotch"/>
+    <n v="4867"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="3"/>
+    <n v="568563.84"/>
+  </r>
+  <r>
+    <s v="Bombay Sapphire Gin"/>
+    <n v="28233"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="94"/>
+    <x v="3"/>
+    <n v="690740.18"/>
+  </r>
+  <r>
+    <s v="Bacardi Limon"/>
+    <n v="43137"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="70"/>
+    <x v="3"/>
+    <n v="771161.8"/>
+  </r>
+  <r>
+    <s v="Bacardi Superior Rum"/>
+    <n v="43126"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="6"/>
+    <n v="971856.24"/>
+  </r>
+  <r>
+    <s v="Bacardi Superior Rum"/>
+    <n v="43128"/>
+    <n v="6"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="0"/>
+    <n v="1703967.5"/>
+  </r>
+  <r>
+    <s v="Bacardi Superior Rum"/>
+    <n v="43127"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="3"/>
+    <n v="1912471.22"/>
+  </r>
+  <r>
+    <s v="Grey Goose Vodka"/>
+    <n v="34433"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="6"/>
+    <n v="1974172.58"/>
+  </r>
+  <r>
+    <s v="Grey Goose Vodka"/>
+    <n v="34422"/>
+    <n v="6"/>
+    <n v="1"/>
+    <n v="80"/>
+    <x v="3"/>
+    <n v="3153668.04"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1CEE9EEA-FE89-4EAB-A2AF-E8C2A0F57877}" name="PivotTable8" cacheId="19" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="21">
+  <location ref="A3:C14" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="7">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="ascending">
+      <items count="11">
+        <item x="1"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="7"/>
+        <item x="9"/>
+        <item x="8"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField dataField="1" numFmtId="8" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="5"/>
+  </rowFields>
+  <rowItems count="11">
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="Sum of total_revenue" fld="6" baseField="0" baseItem="0" numFmtId="8"/>
+    <dataField name="Count of item_description" fld="0" subtotal="count" baseField="5" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="2">
+    <chartFormat chart="12" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="12" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1194,6 +3739,245 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C3A6E8F-9E09-4AB2-A225-4EB671B242EB}">
+  <dimension ref="A3:D24"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
+        <v>100</v>
+      </c>
+      <c r="B4" s="1">
+        <v>316.8</v>
+      </c>
+      <c r="C4" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>603</v>
+      </c>
+      <c r="B5" s="1">
+        <v>537.9</v>
+      </c>
+      <c r="C5" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>50</v>
+      </c>
+      <c r="B6" s="1">
+        <v>1398.12</v>
+      </c>
+      <c r="C6" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <v>600</v>
+      </c>
+      <c r="B7" s="1">
+        <v>99407.52</v>
+      </c>
+      <c r="C7" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
+        <v>500</v>
+      </c>
+      <c r="B8" s="1">
+        <v>220298.14</v>
+      </c>
+      <c r="C8" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
+        <v>200</v>
+      </c>
+      <c r="B9" s="1">
+        <v>427550.06999999995</v>
+      </c>
+      <c r="C9" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
+        <v>375</v>
+      </c>
+      <c r="B10" s="1">
+        <v>867088.47</v>
+      </c>
+      <c r="C10" s="4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
+        <v>1750</v>
+      </c>
+      <c r="B11" s="1">
+        <v>4279176.76</v>
+      </c>
+      <c r="C11" s="4">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
+        <v>750</v>
+      </c>
+      <c r="B12" s="1">
+        <v>7375837.2800000003</v>
+      </c>
+      <c r="C12" s="4">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="3">
+        <v>1000</v>
+      </c>
+      <c r="B13" s="1">
+        <v>7953660.1600000001</v>
+      </c>
+      <c r="C13" s="4">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B14" s="1">
+        <v>21225271.219999999</v>
+      </c>
+      <c r="C14" s="4">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B16" t="s">
+        <v>98</v>
+      </c>
+      <c r="C16" t="s">
+        <v>99</v>
+      </c>
+      <c r="D16" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="6">
+        <v>375</v>
+      </c>
+      <c r="B17" s="5">
+        <v>867088.47</v>
+      </c>
+      <c r="C17">
+        <v>11</v>
+      </c>
+      <c r="D17" s="5">
+        <f t="shared" ref="D17:D20" si="0">B17/C17</f>
+        <v>78826.224545454548</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="6">
+        <v>1750</v>
+      </c>
+      <c r="B18" s="5">
+        <v>4279176.76</v>
+      </c>
+      <c r="C18">
+        <v>22</v>
+      </c>
+      <c r="D18" s="5">
+        <f t="shared" si="0"/>
+        <v>194508.03454545455</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="6">
+        <v>750</v>
+      </c>
+      <c r="B19" s="5">
+        <v>7375837.2800000003</v>
+      </c>
+      <c r="C19">
+        <v>53</v>
+      </c>
+      <c r="D19" s="5">
+        <f t="shared" si="0"/>
+        <v>139166.74113207549</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="6">
+        <v>1000</v>
+      </c>
+      <c r="B20" s="5">
+        <v>7953660.1600000001</v>
+      </c>
+      <c r="C20">
+        <v>22</v>
+      </c>
+      <c r="D20" s="5">
+        <f t="shared" si="0"/>
+        <v>361530.00727272726</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B21" s="4"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B22" s="4"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B23" s="4"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B24" s="4"/>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:C14">
+    <sortCondition descending="1" ref="B3"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
+  <drawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACE7B0A3-09F6-486F-BE94-CA5564D6C79D}">
   <dimension ref="A1:G130"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/week-04/Product spec drivers.xlsx
+++ b/week-04/Product spec drivers.xlsx
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="19" r:id="rId3"/>
+    <pivotCache cacheId="0" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -831,14 +831,13 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="42" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
@@ -1399,6 +1398,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="1026216255"/>
+        <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
@@ -3285,7 +3285,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1CEE9EEA-FE89-4EAB-A2AF-E8C2A0F57877}" name="PivotTable8" cacheId="19" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="21">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1CEE9EEA-FE89-4EAB-A2AF-E8C2A0F57877}" name="PivotTable8" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="21">
   <location ref="A3:C14" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="7">
     <pivotField dataField="1" showAll="0"/>
@@ -3740,7 +3740,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C3A6E8F-9E09-4AB2-A225-4EB671B242EB}">
-  <dimension ref="A3:D24"/>
+  <dimension ref="A3:D20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
@@ -3767,7 +3767,7 @@
       <c r="B4" s="1">
         <v>316.8</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4">
         <v>1</v>
       </c>
     </row>
@@ -3778,7 +3778,7 @@
       <c r="B5" s="1">
         <v>537.9</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5">
         <v>1</v>
       </c>
     </row>
@@ -3789,7 +3789,7 @@
       <c r="B6" s="1">
         <v>1398.12</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6">
         <v>3</v>
       </c>
     </row>
@@ -3800,7 +3800,7 @@
       <c r="B7" s="1">
         <v>99407.52</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7">
         <v>5</v>
       </c>
     </row>
@@ -3811,7 +3811,7 @@
       <c r="B8" s="1">
         <v>220298.14</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8">
         <v>4</v>
       </c>
     </row>
@@ -3822,7 +3822,7 @@
       <c r="B9" s="1">
         <v>427550.06999999995</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9">
         <v>7</v>
       </c>
     </row>
@@ -3833,7 +3833,7 @@
       <c r="B10" s="1">
         <v>867088.47</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10">
         <v>11</v>
       </c>
     </row>
@@ -3844,7 +3844,7 @@
       <c r="B11" s="1">
         <v>4279176.76</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11">
         <v>22</v>
       </c>
     </row>
@@ -3855,7 +3855,7 @@
       <c r="B12" s="1">
         <v>7375837.2800000003</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12">
         <v>53</v>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       <c r="B13" s="1">
         <v>7953660.1600000001</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13">
         <v>22</v>
       </c>
     </row>
@@ -3877,12 +3877,12 @@
       <c r="B14" s="1">
         <v>21225271.219999999</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14">
         <v>129</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="5" t="s">
         <v>101</v>
       </c>
       <c r="B16" t="s">
@@ -3896,76 +3896,64 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="6">
+      <c r="A17" s="5">
         <v>375</v>
       </c>
-      <c r="B17" s="5">
+      <c r="B17" s="4">
         <v>867088.47</v>
       </c>
       <c r="C17">
         <v>11</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D17" s="4">
         <f t="shared" ref="D17:D20" si="0">B17/C17</f>
         <v>78826.224545454548</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="6">
+      <c r="A18" s="5">
         <v>1750</v>
       </c>
-      <c r="B18" s="5">
+      <c r="B18" s="4">
         <v>4279176.76</v>
       </c>
       <c r="C18">
         <v>22</v>
       </c>
-      <c r="D18" s="5">
+      <c r="D18" s="4">
         <f t="shared" si="0"/>
         <v>194508.03454545455</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="6">
+      <c r="A19" s="5">
         <v>750</v>
       </c>
-      <c r="B19" s="5">
+      <c r="B19" s="4">
         <v>7375837.2800000003</v>
       </c>
       <c r="C19">
         <v>53</v>
       </c>
-      <c r="D19" s="5">
+      <c r="D19" s="4">
         <f t="shared" si="0"/>
         <v>139166.74113207549</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="6">
+      <c r="A20" s="5">
         <v>1000</v>
       </c>
-      <c r="B20" s="5">
+      <c r="B20" s="4">
         <v>7953660.1600000001</v>
       </c>
       <c r="C20">
         <v>22</v>
       </c>
-      <c r="D20" s="5">
+      <c r="D20" s="4">
         <f t="shared" si="0"/>
         <v>361530.00727272726</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B21" s="4"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B22" s="4"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B23" s="4"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B24" s="4"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:C14">
